--- a/pipeline_output/DELHI_2W_H&M.xlsx
+++ b/pipeline_output/DELHI_2W_H&M.xlsx
@@ -736,12 +736,12 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -853,12 +853,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -980,12 +980,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -1234,12 +1234,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -1605,12 +1605,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -1722,12 +1722,12 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -1849,12 +1849,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -1976,12 +1976,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -2474,12 +2474,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -2708,12 +2708,12 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -2835,12 +2835,12 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -3440,12 +3440,12 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -3567,12 +3567,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -3811,12 +3811,12 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="AM29" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN29" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO29" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN30" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN31" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="AM32" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN32" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO32" t="inlineStr">
@@ -4563,12 +4563,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN33" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
@@ -4680,12 +4680,12 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
@@ -4934,12 +4934,12 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
@@ -5051,12 +5051,12 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN37" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO37" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN38" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
@@ -5295,12 +5295,12 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN39" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
@@ -5422,12 +5422,12 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN40" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
@@ -5549,12 +5549,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN41" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
@@ -5676,12 +5676,12 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN42" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO42" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN43" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO43" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="AM44" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN44" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO44" t="inlineStr">
@@ -6027,12 +6027,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN45" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
@@ -6144,12 +6144,12 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN46" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO46" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="AM47" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN47" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO47" t="inlineStr">
@@ -6388,12 +6388,12 @@
       </c>
       <c r="AM48" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN48" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO48" t="inlineStr">
@@ -6515,12 +6515,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN49" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
@@ -6642,12 +6642,12 @@
       </c>
       <c r="AM50" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN50" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO50" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN51" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
@@ -6886,12 +6886,12 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN52" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN53" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN54" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO54" t="inlineStr">
@@ -7257,12 +7257,12 @@
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN55" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
@@ -7384,12 +7384,12 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN56" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO56" t="inlineStr">
@@ -7511,12 +7511,12 @@
       </c>
       <c r="AM57" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN57" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO57" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="AM58" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN58" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN59" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN60" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO60" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
@@ -8009,12 +8009,12 @@
       </c>
       <c r="AM61" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN61" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO61" t="inlineStr">
@@ -8071,7 +8071,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
@@ -8136,12 +8136,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN62" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN63" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
@@ -8325,7 +8325,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN64" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="AM65" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN65" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO65" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN66" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
@@ -8706,7 +8706,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="AM67" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN67" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO67" t="inlineStr">
@@ -8833,7 +8833,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN68" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
@@ -8960,7 +8960,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
@@ -9015,12 +9015,12 @@
       </c>
       <c r="AM69" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN69" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO69" t="inlineStr">
@@ -9077,7 +9077,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -9132,12 +9132,12 @@
       </c>
       <c r="AM70" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN70" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO70" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
@@ -9249,12 +9249,12 @@
       </c>
       <c r="AM71" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN71" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO71" t="inlineStr">
@@ -9311,7 +9311,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -9366,12 +9366,12 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN72" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN73" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN74" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
@@ -9662,7 +9662,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="AM75" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN75" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO75" t="inlineStr">
@@ -9779,7 +9779,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -9834,12 +9834,12 @@
       </c>
       <c r="AM76" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN76" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -9896,7 +9896,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -9951,12 +9951,12 @@
       </c>
       <c r="AM77" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN77" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO77" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN78" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO78" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -10185,12 +10185,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN79" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -10302,12 +10302,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -10364,7 +10364,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -10419,12 +10419,12 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
@@ -10481,7 +10481,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -10598,7 +10598,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -10653,12 +10653,12 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN83" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -10715,7 +10715,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>DELHI</t>
+          <t>DELHI, UTTAR PRADESH</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -10770,12 +10770,12 @@
       </c>
       <c r="AM84" t="inlineStr">
         <is>
-          <t>2026-02-01</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="AN84" t="inlineStr">
         <is>
-          <t>2026-02-28</t>
+          <t>2026-01-31</t>
         </is>
       </c>
       <c r="AO84" t="inlineStr">
